--- a/Decks/JhoiraBichao.xlsx
+++ b/Decks/JhoiraBichao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C464176-DC72-46EE-A9F2-162D48EA10BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3A4149-B027-42CB-A932-8334738C8171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F75954E-9EEB-4531-B827-821D6BA36D92}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
   <si>
     <t>Função</t>
   </si>
@@ -320,13 +320,16 @@
     <t>Crawlspace</t>
   </si>
   <si>
-    <t>Portent of Calamity</t>
-  </si>
-  <si>
     <t>Mana Sculpt</t>
   </si>
   <si>
     <t>Sleight of Hand</t>
+  </si>
+  <si>
+    <t>Mind's Dilation</t>
+  </si>
+  <si>
+    <t>Improvisation Capstone</t>
   </si>
 </sst>
 </file>
@@ -767,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B65" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1274,17 +1277,17 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B37" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1311,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1326,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,10 +1344,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1356,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1371,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1386,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1398,14 +1401,15 @@
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -1416,26 +1420,25 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F46"/>
+        <v>31</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1447,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1462,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1477,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1489,13 +1492,13 @@
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1504,13 +1507,13 @@
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1522,11 +1525,12 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -1537,26 +1541,26 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F55"/>
     </row>
@@ -1569,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="F56"/>
     </row>
@@ -1585,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="F57"/>
     </row>
@@ -1601,12 +1605,11 @@
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -1617,11 +1620,12 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F59"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -1632,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1648,27 +1652,27 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
-      </c>
-      <c r="F61"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -1676,13 +1680,13 @@
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F63"/>
     </row>
@@ -1692,13 +1696,13 @@
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F64"/>
     </row>
@@ -1711,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F65"/>
     </row>
@@ -1723,30 +1727,30 @@
         <v>49</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
+        <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
-      </c>
-      <c r="F66"/>
+        <v>56</v>
+      </c>
+      <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>49</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D67" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F67" s="4"/>
     </row>
@@ -1756,13 +1760,13 @@
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F68" s="4"/>
     </row>
@@ -1775,12 +1779,11 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D69" t="s">
-        <v>58</v>
-      </c>
-      <c r="F69" s="4"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -1788,13 +1791,13 @@
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -1851,43 +1854,42 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="F74"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>49</v>
       </c>
       <c r="B75" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C75&lt;&gt;D75</f>
+        <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
-      </c>
-      <c r="F75"/>
+        <v>97</v>
+      </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>49</v>
       </c>
       <c r="B76" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
-      </c>
-      <c r="F76"/>
+        <v>96</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1898,12 +1900,12 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D77" t="s">
-        <v>67</v>
-      </c>
-      <c r="E77" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1914,11 +1916,12 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D78" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="E78" s="4"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -1929,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -1944,12 +1947,11 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
-      </c>
-      <c r="E80" s="4"/>
+        <v>69</v>
+      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -1957,29 +1959,29 @@
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
-      </c>
-      <c r="F81" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="E81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F82" s="4"/>
     </row>
@@ -1992,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F83" s="4"/>
     </row>
@@ -2008,10 +2010,10 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F84" s="4"/>
     </row>
@@ -2024,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F85" s="4"/>
     </row>
@@ -2040,11 +2042,12 @@
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
@@ -2055,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2067,13 +2070,13 @@
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2082,13 +2085,13 @@
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D89" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,12 +2118,11 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D91" t="s">
-        <v>84</v>
-      </c>
-      <c r="F91"/>
+        <v>83</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -2131,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F92"/>
     </row>
@@ -2147,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F93"/>
     </row>
@@ -2163,11 +2165,12 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D94" t="s">
-        <v>87</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -2178,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -2193,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -2208,12 +2211,11 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F97"/>
+        <v>89</v>
+      </c>
+      <c r="D97" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -2224,11 +2226,12 @@
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
@@ -2239,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D99" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -2254,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="D100" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -2269,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D101" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/JhoiraBichao.xlsx
+++ b/Decks/JhoiraBichao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3A4149-B027-42CB-A932-8334738C8171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E805A8A-2987-4B68-9D5C-6A8DE1ECFE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F75954E-9EEB-4531-B827-821D6BA36D92}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="99">
   <si>
     <t>Função</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>Improvisation Capstone</t>
+  </si>
+  <si>
+    <t>Stormcarved Coast</t>
   </si>
 </sst>
 </file>
@@ -894,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1119,10 +1122,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/JhoiraBichao.xlsx
+++ b/Decks/JhoiraBichao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E805A8A-2987-4B68-9D5C-6A8DE1ECFE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A3065D-61F2-410D-91B6-1E88EEC11C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F75954E-9EEB-4531-B827-821D6BA36D92}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="97">
   <si>
     <t>Função</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Aminatou's Augury</t>
   </si>
   <si>
-    <t>Consecrated Sphinx</t>
-  </si>
-  <si>
     <t>Nezahal, Primal Tide</t>
   </si>
   <si>
@@ -278,9 +275,6 @@
     <t>Paradox Haze</t>
   </si>
   <si>
-    <t>Divergent Transformations</t>
-  </si>
-  <si>
     <t>The Tenth Doctor</t>
   </si>
   <si>
@@ -323,9 +317,6 @@
     <t>Mana Sculpt</t>
   </si>
   <si>
-    <t>Sleight of Hand</t>
-  </si>
-  <si>
     <t>Mind's Dilation</t>
   </si>
   <si>
@@ -333,6 +324,9 @@
   </si>
   <si>
     <t>Stormcarved Coast</t>
+  </si>
+  <si>
+    <t>Shivan Reef</t>
   </si>
 </sst>
 </file>
@@ -897,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -912,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1576,10 +1570,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F56"/>
     </row>
@@ -1683,10 +1677,10 @@
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D63" t="s">
         <v>52</v>
@@ -1731,10 +1725,10 @@
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" ref="B66:B101" si="1">C66&lt;&gt;D66</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
         <v>56</v>
@@ -1766,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D68" t="s">
         <v>58</v>
@@ -1870,13 +1864,13 @@
       </c>
       <c r="B75" s="5" t="b">
         <f>C75&lt;&gt;D75</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -1888,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D76" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -1950,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -1965,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E81" s="4"/>
     </row>
@@ -1981,304 +1975,304 @@
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" t="s">
         <v>71</v>
-      </c>
-      <c r="D82" t="s">
-        <v>72</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B83" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="D83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D89" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D92" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F94"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D95" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D97" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D100" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
